--- a/VISION_RCS_MAPPING.xlsx
+++ b/VISION_RCS_MAPPING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longn\PycharmProjects\PIDVN25006\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7765FB32-8183-4DAE-BE9C-15C36E85C068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1255B97B-24FA-47EE-B939-B7984FFF8961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E014B776-88C9-4C05-901C-C8B9F118C302}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="132">
   <si>
     <t>site thực tế</t>
   </si>
@@ -309,6 +309,129 @@
   </si>
   <si>
     <t>FG-B6</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>cam1</t>
+  </si>
+  <si>
+    <t>Khu , Camera 1, Vùng A1, object TROLLEY</t>
+  </si>
+  <si>
+    <t>Khu , Camera 1, Vùng A2, object TROLLEY</t>
+  </si>
+  <si>
+    <t>Khu , Camera 1, Vùng A3, object TROLLEY</t>
+  </si>
+  <si>
+    <t>Khu , Camera 1, Vùng B1, object TROLLEY</t>
+  </si>
+  <si>
+    <t>Khu , Camera 1, Vùng B2, object TROLLEY</t>
+  </si>
+  <si>
+    <t>Khu , Camera 1, Vùng B3, object TROLLEY</t>
+  </si>
+  <si>
+    <t>cam2</t>
+  </si>
+  <si>
+    <t>cam3</t>
+  </si>
+  <si>
+    <t>cam6</t>
+  </si>
+  <si>
+    <t>cam7</t>
+  </si>
+  <si>
+    <t>cam8</t>
   </si>
 </sst>
 </file>
@@ -331,12 +454,18 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -351,9 +480,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -690,59 +822,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFD9B5C-E48E-44FD-AE82-247842BF08FC}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="22.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.09765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.8984375" style="1"/>
-    <col min="9" max="9" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.19921875" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.09765625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="10.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>53</v>
       </c>
     </row>
@@ -751,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -777,7 +909,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>15</v>
@@ -803,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -829,7 +961,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
@@ -855,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -881,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
@@ -907,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>20</v>
@@ -933,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>21</v>
@@ -959,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>22</v>
@@ -985,7 +1117,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
@@ -1011,7 +1143,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>24</v>
@@ -1037,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>25</v>
@@ -1063,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>26</v>
@@ -1089,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>27</v>
@@ -1115,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -1141,7 +1273,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1167,7 +1299,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>30</v>
@@ -1193,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>31</v>
@@ -1219,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1245,7 +1377,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>33</v>
@@ -1271,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>34</v>
@@ -1297,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>35</v>
@@ -1323,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>36</v>
@@ -1349,7 +1481,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>37</v>
@@ -1375,7 +1507,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>38</v>
@@ -1401,7 +1533,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>39</v>
@@ -1427,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>40</v>
@@ -1453,7 +1585,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>41</v>
@@ -1479,7 +1611,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>42</v>
@@ -1505,7 +1637,7 @@
         <v>11</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>43</v>
@@ -1531,7 +1663,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>44</v>
@@ -1557,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>45</v>
@@ -1583,7 +1715,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>46</v>
@@ -1609,7 +1741,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>47</v>
@@ -1635,7 +1767,7 @@
         <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>48</v>
@@ -1661,7 +1793,7 @@
         <v>12</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>49</v>
@@ -1687,7 +1819,7 @@
         <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>49</v>
@@ -1706,6 +1838,227 @@
       </c>
       <c r="L38" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/VISION_RCS_MAPPING.xlsx
+++ b/VISION_RCS_MAPPING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longn\PycharmProjects\PIDVN25006\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1255B97B-24FA-47EE-B939-B7984FFF8961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420A070E-643A-43C7-821E-CA586060F495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E014B776-88C9-4C05-901C-C8B9F118C302}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="120">
   <si>
     <t>site thực tế</t>
   </si>
   <si>
-    <t>Mã bussiness trên UI RCS</t>
-  </si>
-  <si>
     <t>method</t>
   </si>
   <si>
@@ -191,126 +188,6 @@
     <t xml:space="preserve">lockPosition </t>
   </si>
   <si>
-    <t>camera-id</t>
-  </si>
-  <si>
-    <t>zone-id</t>
-  </si>
-  <si>
-    <t>unknown-action</t>
-  </si>
-  <si>
-    <t>PK-A1</t>
-  </si>
-  <si>
-    <t>PK-A2</t>
-  </si>
-  <si>
-    <t>PK-A3</t>
-  </si>
-  <si>
-    <t>PK-A4</t>
-  </si>
-  <si>
-    <t>PK-B1</t>
-  </si>
-  <si>
-    <t>PK-B2</t>
-  </si>
-  <si>
-    <t>PK-B3</t>
-  </si>
-  <si>
-    <t>PK-B4</t>
-  </si>
-  <si>
-    <t>PK-C1</t>
-  </si>
-  <si>
-    <t>PK-C2</t>
-  </si>
-  <si>
-    <t>PK-C3</t>
-  </si>
-  <si>
-    <t>PK-C4</t>
-  </si>
-  <si>
-    <t>PK-D1</t>
-  </si>
-  <si>
-    <t>PK-D2</t>
-  </si>
-  <si>
-    <t>PK-D3</t>
-  </si>
-  <si>
-    <t>PK-D4</t>
-  </si>
-  <si>
-    <t>PK-E1</t>
-  </si>
-  <si>
-    <t>PK-E2</t>
-  </si>
-  <si>
-    <t>PK-E3</t>
-  </si>
-  <si>
-    <t>PK-E4</t>
-  </si>
-  <si>
-    <t>PK-F1</t>
-  </si>
-  <si>
-    <t>PK-F2</t>
-  </si>
-  <si>
-    <t>PK-F3</t>
-  </si>
-  <si>
-    <t>PK-F4</t>
-  </si>
-  <si>
-    <t>FG-A1</t>
-  </si>
-  <si>
-    <t>FG-A2</t>
-  </si>
-  <si>
-    <t>FG-A3</t>
-  </si>
-  <si>
-    <t>FG-A4</t>
-  </si>
-  <si>
-    <t>FG-A5</t>
-  </si>
-  <si>
-    <t>FG-A6</t>
-  </si>
-  <si>
-    <t>FG-A7</t>
-  </si>
-  <si>
-    <t>FG-B1</t>
-  </si>
-  <si>
-    <t>FG-B2</t>
-  </si>
-  <si>
-    <t>FG-B3</t>
-  </si>
-  <si>
-    <t>FG-B4</t>
-  </si>
-  <si>
-    <t>FG-B5</t>
-  </si>
-  <si>
-    <t>FG-B6</t>
-  </si>
-  <si>
     <t>A1</t>
   </si>
   <si>
@@ -398,40 +275,127 @@
     <t>B6</t>
   </si>
   <si>
-    <t>cam1</t>
-  </si>
-  <si>
-    <t>Khu , Camera 1, Vùng A1, object TROLLEY</t>
-  </si>
-  <si>
-    <t>Khu , Camera 1, Vùng A2, object TROLLEY</t>
-  </si>
-  <si>
-    <t>Khu , Camera 1, Vùng A3, object TROLLEY</t>
-  </si>
-  <si>
-    <t>Khu , Camera 1, Vùng B1, object TROLLEY</t>
-  </si>
-  <si>
-    <t>Khu , Camera 1, Vùng B2, object TROLLEY</t>
-  </si>
-  <si>
-    <t>Khu , Camera 1, Vùng B3, object TROLLEY</t>
-  </si>
-  <si>
-    <t>cam2</t>
-  </si>
-  <si>
-    <t>cam3</t>
-  </si>
-  <si>
-    <t>cam6</t>
-  </si>
-  <si>
-    <t>cam7</t>
-  </si>
-  <si>
-    <t>cam8</t>
+    <t>camera_id</t>
+  </si>
+  <si>
+    <t>zone_id</t>
+  </si>
+  <si>
+    <t>unknown_action</t>
+  </si>
+  <si>
+    <t>PK_A1</t>
+  </si>
+  <si>
+    <t>PK_A2</t>
+  </si>
+  <si>
+    <t>PK_A3</t>
+  </si>
+  <si>
+    <t>PK_A4</t>
+  </si>
+  <si>
+    <t>PK_B1</t>
+  </si>
+  <si>
+    <t>PK_B2</t>
+  </si>
+  <si>
+    <t>PK_B3</t>
+  </si>
+  <si>
+    <t>PK_B4</t>
+  </si>
+  <si>
+    <t>PK_C1</t>
+  </si>
+  <si>
+    <t>PK_C2</t>
+  </si>
+  <si>
+    <t>PK_C3</t>
+  </si>
+  <si>
+    <t>PK_C4</t>
+  </si>
+  <si>
+    <t>PK_D1</t>
+  </si>
+  <si>
+    <t>PK_D2</t>
+  </si>
+  <si>
+    <t>PK_D3</t>
+  </si>
+  <si>
+    <t>PK_D4</t>
+  </si>
+  <si>
+    <t>PK_E1</t>
+  </si>
+  <si>
+    <t>PK_E2</t>
+  </si>
+  <si>
+    <t>PK_E3</t>
+  </si>
+  <si>
+    <t>PK_E4</t>
+  </si>
+  <si>
+    <t>PK_F1</t>
+  </si>
+  <si>
+    <t>PK_F2</t>
+  </si>
+  <si>
+    <t>PK_F3</t>
+  </si>
+  <si>
+    <t>PK_F4</t>
+  </si>
+  <si>
+    <t>FG_A1</t>
+  </si>
+  <si>
+    <t>FG_A2</t>
+  </si>
+  <si>
+    <t>FG_A3</t>
+  </si>
+  <si>
+    <t>FG_A4</t>
+  </si>
+  <si>
+    <t>FG_A5</t>
+  </si>
+  <si>
+    <t>FG_A6</t>
+  </si>
+  <si>
+    <t>FG_A7</t>
+  </si>
+  <si>
+    <t>FG_B1</t>
+  </si>
+  <si>
+    <t>FG_B2</t>
+  </si>
+  <si>
+    <t>FG_B3</t>
+  </si>
+  <si>
+    <t>FG_B4</t>
+  </si>
+  <si>
+    <t>FG_B5</t>
+  </si>
+  <si>
+    <t>FG_B6</t>
+  </si>
+  <si>
+    <t>mã trên RCS</t>
   </si>
 </sst>
 </file>
@@ -822,13 +786,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFD9B5C-E48E-44FD-AE82-247842BF08FC}">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="22.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.09765625" style="1" customWidth="1"/>
     <col min="3" max="3" width="48.09765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.19921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.3984375" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -842,1223 +806,1002 @@
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="L1" s="2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="J19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="J20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="J21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="J22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="J23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="J24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="J26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="J27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="J30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="J31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="J32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="J33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="J34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="J35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="J37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="J38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/VISION_RCS_MAPPING.xlsx
+++ b/VISION_RCS_MAPPING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longn\PycharmProjects\PIDVN25006\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420A070E-643A-43C7-821E-CA586060F495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED908A2-9336-4622-9A60-6D01CD300192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E014B776-88C9-4C05-901C-C8B9F118C302}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="117">
   <si>
     <t>site thực tế</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Khu FG, Camera 09, Vùng A6, object PALLET</t>
   </si>
   <si>
-    <t>Khu FG, Camera 09, Vùng A7, object PALLET</t>
-  </si>
-  <si>
     <t>Khu FG, Camera 10, Vùng B1, object PALLET</t>
   </si>
   <si>
@@ -266,9 +263,6 @@
     <t>A6</t>
   </si>
   <si>
-    <t>A7</t>
-  </si>
-  <si>
     <t>B5</t>
   </si>
   <si>
@@ -372,9 +366,6 @@
   </si>
   <si>
     <t>FG_A6</t>
-  </si>
-  <si>
-    <t>FG_A7</t>
   </si>
   <si>
     <t>FG_B1</t>
@@ -786,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFD9B5C-E48E-44FD-AE82-247842BF08FC}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="22.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -806,16 +797,16 @@
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -839,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,7 +838,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -856,16 +847,16 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -873,7 +864,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>14</v>
@@ -882,16 +873,16 @@
         <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -899,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
@@ -908,16 +899,16 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -925,7 +916,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -934,16 +925,16 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -951,7 +942,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
@@ -960,16 +951,16 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -977,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
@@ -986,16 +977,16 @@
         <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1003,7 +994,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>19</v>
@@ -1012,16 +1003,16 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1029,7 +1020,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>20</v>
@@ -1038,16 +1029,16 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1055,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>21</v>
@@ -1064,16 +1055,16 @@
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1081,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>22</v>
@@ -1090,16 +1081,16 @@
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1107,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>23</v>
@@ -1116,16 +1107,16 @@
         <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1133,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>24</v>
@@ -1142,16 +1133,16 @@
         <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1159,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
@@ -1168,16 +1159,16 @@
         <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1185,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>26</v>
@@ -1194,16 +1185,16 @@
         <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1211,7 +1202,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>27</v>
@@ -1220,16 +1211,16 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1237,7 +1228,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>28</v>
@@ -1246,16 +1237,16 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1263,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1272,16 +1263,16 @@
         <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1289,7 +1280,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>
@@ -1298,16 +1289,16 @@
         <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1315,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>31</v>
@@ -1324,16 +1315,16 @@
         <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1341,7 +1332,7 @@
         <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -1350,16 +1341,16 @@
         <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1367,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>33</v>
@@ -1376,16 +1367,16 @@
         <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1393,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>34</v>
@@ -1402,16 +1393,16 @@
         <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1419,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>35</v>
@@ -1428,16 +1419,16 @@
         <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1445,7 +1436,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>36</v>
@@ -1454,16 +1445,16 @@
         <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1471,7 +1462,7 @@
         <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>37</v>
@@ -1480,16 +1471,16 @@
         <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1497,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>38</v>
@@ -1506,16 +1497,16 @@
         <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1523,7 +1514,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>39</v>
@@ -1532,16 +1523,16 @@
         <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1549,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>40</v>
@@ -1558,16 +1549,16 @@
         <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1575,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>41</v>
@@ -1584,16 +1575,16 @@
         <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1601,7 +1592,7 @@
         <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>42</v>
@@ -1610,24 +1601,24 @@
         <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>43</v>
@@ -1636,16 +1627,16 @@
         <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1662,16 +1653,16 @@
         <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1688,16 +1679,16 @@
         <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1714,16 +1705,16 @@
         <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1731,7 +1722,7 @@
         <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>47</v>
@@ -1740,16 +1731,16 @@
         <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1757,51 +1748,25 @@
         <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/VISION_RCS_MAPPING.xlsx
+++ b/VISION_RCS_MAPPING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longn\PycharmProjects\PIDVN25006\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED908A2-9336-4622-9A60-6D01CD300192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E623A3-D2CE-4779-AB1C-B29CA24E7082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E014B776-88C9-4C05-901C-C8B9F118C302}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="117">
   <si>
     <t>site thực tế</t>
   </si>
@@ -386,7 +386,7 @@
     <t>FG_B6</t>
   </si>
   <si>
-    <t>mã trên RCS</t>
+    <t>Pallet_Pana</t>
   </si>
 </sst>
 </file>
@@ -777,25 +777,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFD9B5C-E48E-44FD-AE82-247842BF08FC}">
-  <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="22.2" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultColWidth="10.296875" defaultRowHeight="22.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.09765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.19921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.8984375" style="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.19921875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.09765625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.8984375" style="1"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>77</v>
       </c>
@@ -806,34 +805,31 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -843,23 +839,23 @@
       <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -869,23 +865,23 @@
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -895,23 +891,23 @@
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -921,23 +917,23 @@
       <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="I5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -947,23 +943,23 @@
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="H6" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="I6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,23 +969,23 @@
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="H7" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="I7" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -999,23 +995,23 @@
       <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="H8" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="I8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1025,23 +1021,23 @@
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="H9" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="I9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1051,23 +1047,23 @@
       <c r="C10" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="H10" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1077,23 +1073,23 @@
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="H11" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="I11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1103,23 +1099,23 @@
       <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="H12" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="I12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1129,23 +1125,23 @@
       <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="H13" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="I13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1155,23 +1151,23 @@
       <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="H14" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="I14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,23 +1177,23 @@
       <c r="C15" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="H15" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="I15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
@@ -1207,23 +1203,23 @@
       <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="H16" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="I16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1233,23 +1229,23 @@
       <c r="C17" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="H17" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="I17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,23 +1255,23 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
         <v>96</v>
       </c>
+      <c r="H18" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="I18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
@@ -1285,23 +1281,23 @@
       <c r="C19" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="H19" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="I19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -1311,23 +1307,23 @@
       <c r="C20" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="H20" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="I20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,23 +1333,23 @@
       <c r="C21" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="H21" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="I21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,23 +1359,23 @@
       <c r="C22" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="H22" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="I22" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
@@ -1389,23 +1385,23 @@
       <c r="C23" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="H23" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="I23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1415,23 +1411,23 @@
       <c r="C24" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="D24" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="H24" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="I24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
@@ -1441,23 +1437,23 @@
       <c r="C25" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="D25" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="H25" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="I25" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
@@ -1467,23 +1463,23 @@
       <c r="C26" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="H26" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="I26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -1493,23 +1489,23 @@
       <c r="C27" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="H27" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="I27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
@@ -1519,23 +1515,23 @@
       <c r="C28" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="H28" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="I28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -1545,23 +1541,23 @@
       <c r="C29" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="H29" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="I29" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>10</v>
       </c>
@@ -1571,23 +1567,23 @@
       <c r="C30" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="H30" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I30" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -1597,23 +1593,23 @@
       <c r="C31" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="1" t="s">
         <v>109</v>
       </c>
+      <c r="H31" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="I31" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
@@ -1623,23 +1619,23 @@
       <c r="C32" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="D32" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="H32" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="I32" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1649,23 +1645,23 @@
       <c r="C33" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="D33" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="H33" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="I33" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1675,23 +1671,23 @@
       <c r="C34" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D34" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="H34" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="I34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
@@ -1701,23 +1697,23 @@
       <c r="C35" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="D35" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="H35" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="I35" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
@@ -1727,23 +1723,23 @@
       <c r="C36" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D36" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="H36" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="I36" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>11</v>
       </c>
@@ -1753,19 +1749,19 @@
       <c r="C37" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D37" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="H37" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="I37" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>48</v>
       </c>
     </row>
